--- a/001_Can_SapCoupa_CIBC_Performer/Data/GMCAN_RPA001_Performer_Config.xlsx
+++ b/001_Can_SapCoupa_CIBC_Performer/Data/GMCAN_RPA001_Performer_Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\grmusarpadev09\OneDrive - insidemedia.net\Desktop\Linktera\Aniket\New_001_Can_SapCoupa_CIBC\001_Can_SapCoupa_CIBC\001_Can_SapCoupa_CIBC_Performer\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://insidemedia-my.sharepoint.com/personal/forms_membership__nycgrm_ar_service_groupm_com/Documents/Desktop/Aniket Code/Coupa_CIBC/001_Can_SapCoupa_CIBC_Performer/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{076E4E46-6E37-4942-99F1-17B9D8514AA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{90703517-B46F-45E7-A1DE-1AAE02570C0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{189C4BC2-9A39-4C86-BBAF-0FF079D74314}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20700" windowHeight="8745" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="8745" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="86">
   <si>
     <t>Name</t>
   </si>
@@ -281,10 +281,7 @@
     <t>aniketni@cybage.com</t>
   </si>
   <si>
-    <t>C:\Users\grmusarpadev09\OneDrive - insidemedia.net\Documents\ProcessBusinessFiles\GMCAN_RPA001_AR_CIBC_Coupa\ReportExcels\</t>
-  </si>
-  <si>
-    <t>GMCAN_FINANCE_AR</t>
+    <t>C:\Users\grmusarpadev21\OneDrive - insidemedia.net\Documents\ProcessBusinessFiles\GMCAN_RPA001_AR_CIBC_Coupa\ReportExcels\</t>
   </si>
 </sst>
 </file>
@@ -371,9 +368,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -411,7 +408,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -517,7 +514,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -659,7 +656,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3070,9 +3067,6 @@
       <c r="B2" t="s">
         <v>50</v>
       </c>
-      <c r="C2" t="s">
-        <v>86</v>
-      </c>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1">
       <c r="A3" t="s">
@@ -3081,9 +3075,6 @@
       <c r="B3" t="s">
         <v>66</v>
       </c>
-      <c r="C3" t="s">
-        <v>86</v>
-      </c>
       <c r="D3" t="s">
         <v>67</v>
       </c>
@@ -3095,9 +3086,6 @@
       <c r="B4" t="s">
         <v>69</v>
       </c>
-      <c r="C4" t="s">
-        <v>86</v>
-      </c>
       <c r="D4" t="s">
         <v>70</v>
       </c>
@@ -3108,9 +3096,6 @@
       </c>
       <c r="B5" t="s">
         <v>71</v>
-      </c>
-      <c r="C5" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1"/>
@@ -4115,15 +4100,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="7f25b792-b2ba-4b5c-8669-b39a27555406" xsi:nil="true"/>
@@ -4133,6 +4109,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4371,20 +4356,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88DD52F0-380C-4F9B-9C65-D8FAFBB1FD6B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1FDF64E-9575-4071-ADF7-AA8A91CB418F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="7f25b792-b2ba-4b5c-8669-b39a27555406"/>
     <ds:schemaRef ds:uri="649a79cd-06e4-47a3-aac9-21cb806f3675"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88DD52F0-380C-4F9B-9C65-D8FAFBB1FD6B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/001_Can_SapCoupa_CIBC_Performer/Data/GMCAN_RPA001_Performer_Config.xlsx
+++ b/001_Can_SapCoupa_CIBC_Performer/Data/GMCAN_RPA001_Performer_Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://insidemedia-my.sharepoint.com/personal/forms_membership__nycgrm_ar_service_groupm_com/Documents/Desktop/Aniket Code/Coupa_CIBC/001_Can_SapCoupa_CIBC_Performer/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\grmusarpadev09\OneDrive - insidemedia.net\Desktop\Linktera\Aniket\New_001_Can_SapCoupa_CIBC\001_Can_SapCoupa_CIBC\001_Can_SapCoupa_CIBC_Performer\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{90703517-B46F-45E7-A1DE-1AAE02570C0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{189C4BC2-9A39-4C86-BBAF-0FF079D74314}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{076E4E46-6E37-4942-99F1-17B9D8514AA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="8745" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20700" windowHeight="8745" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="87">
   <si>
     <t>Name</t>
   </si>
@@ -281,7 +281,10 @@
     <t>aniketni@cybage.com</t>
   </si>
   <si>
-    <t>C:\Users\grmusarpadev21\OneDrive - insidemedia.net\Documents\ProcessBusinessFiles\GMCAN_RPA001_AR_CIBC_Coupa\ReportExcels\</t>
+    <t>C:\Users\grmusarpadev09\OneDrive - insidemedia.net\Documents\ProcessBusinessFiles\GMCAN_RPA001_AR_CIBC_Coupa\ReportExcels\</t>
+  </si>
+  <si>
+    <t>GMCAN_FINANCE_AR</t>
   </si>
 </sst>
 </file>
@@ -368,9 +371,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -408,7 +411,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -514,7 +517,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -656,7 +659,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3067,6 +3070,9 @@
       <c r="B2" t="s">
         <v>50</v>
       </c>
+      <c r="C2" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1">
       <c r="A3" t="s">
@@ -3075,6 +3081,9 @@
       <c r="B3" t="s">
         <v>66</v>
       </c>
+      <c r="C3" t="s">
+        <v>86</v>
+      </c>
       <c r="D3" t="s">
         <v>67</v>
       </c>
@@ -3086,6 +3095,9 @@
       <c r="B4" t="s">
         <v>69</v>
       </c>
+      <c r="C4" t="s">
+        <v>86</v>
+      </c>
       <c r="D4" t="s">
         <v>70</v>
       </c>
@@ -3096,6 +3108,9 @@
       </c>
       <c r="B5" t="s">
         <v>71</v>
+      </c>
+      <c r="C5" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1"/>
@@ -4100,6 +4115,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="7f25b792-b2ba-4b5c-8669-b39a27555406" xsi:nil="true"/>
@@ -4109,15 +4133,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4356,20 +4371,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88DD52F0-380C-4F9B-9C65-D8FAFBB1FD6B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1FDF64E-9575-4071-ADF7-AA8A91CB418F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="7f25b792-b2ba-4b5c-8669-b39a27555406"/>
     <ds:schemaRef ds:uri="649a79cd-06e4-47a3-aac9-21cb806f3675"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88DD52F0-380C-4F9B-9C65-D8FAFBB1FD6B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
